--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N104_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N104_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>82.77137251127569</v>
+        <v>13.4503480330823</v>
       </c>
       <c r="D2" t="n">
-        <v>22.19160695457708</v>
+        <v>3.606136130118776</v>
       </c>
       <c r="E2" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F2" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>73.5148470745283</v>
+        <v>11.94616264961085</v>
       </c>
       <c r="D3" t="n">
-        <v>8.688485198074067</v>
+        <v>1.411878844687036</v>
       </c>
       <c r="E3" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F3" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>69.77203043166615</v>
+        <v>11.33795494514575</v>
       </c>
       <c r="D4" t="n">
-        <v>12.4447881307855</v>
+        <v>2.022278071252644</v>
       </c>
       <c r="E4" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F4" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.30135885298714</v>
+        <v>8.33647081361041</v>
       </c>
       <c r="D5" t="n">
-        <v>20.16925712021577</v>
+        <v>3.277504282035063</v>
       </c>
       <c r="E5" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F5" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.44484411804616</v>
+        <v>6.409787169182501</v>
       </c>
       <c r="D6" t="n">
-        <v>9.33267606321167</v>
+        <v>1.516559860271896</v>
       </c>
       <c r="E6" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F6" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.3031676244773</v>
+        <v>5.249264738977562</v>
       </c>
       <c r="D7" t="n">
-        <v>16.70745010134367</v>
+        <v>2.714960641468346</v>
       </c>
       <c r="E7" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F7" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>67.79619423983881</v>
+        <v>11.01688156397381</v>
       </c>
       <c r="D8" t="n">
-        <v>50.86064839889043</v>
+        <v>8.264855364819695</v>
       </c>
       <c r="E8" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F8" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.36116944761658</v>
+        <v>7.696190035237695</v>
       </c>
       <c r="D9" t="n">
-        <v>31.42009265139462</v>
+        <v>5.105765055851625</v>
       </c>
       <c r="E9" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F9" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>60.34422748995951</v>
+        <v>9.805936967118422</v>
       </c>
       <c r="D10" t="n">
-        <v>45.27693821126654</v>
+        <v>7.357502459330813</v>
       </c>
       <c r="E10" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F10" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>42.85932986132715</v>
+        <v>6.964641102465663</v>
       </c>
       <c r="D11" t="n">
-        <v>29.35226661700175</v>
+        <v>4.769743325262785</v>
       </c>
       <c r="E11" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F11" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.94438428560142</v>
+        <v>7.46596244641023</v>
       </c>
       <c r="D12" t="n">
-        <v>33.98733424216864</v>
+        <v>5.522941814352404</v>
       </c>
       <c r="E12" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F12" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>26.76241449418088</v>
+        <v>4.348892355304394</v>
       </c>
       <c r="D13" t="n">
-        <v>31.5485736603099</v>
+        <v>5.126643219800359</v>
       </c>
       <c r="E13" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F13" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.71715857849966</v>
+        <v>4.341538269006196</v>
       </c>
       <c r="D14" t="n">
-        <v>17.38870588672996</v>
+        <v>2.825664706593618</v>
       </c>
       <c r="E14" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F14" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>44.44959271165715</v>
+        <v>7.223058815644286</v>
       </c>
       <c r="D15" t="n">
-        <v>38.10001458150786</v>
+        <v>6.191252369495027</v>
       </c>
       <c r="E15" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F15" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>31.37837710902041</v>
+        <v>5.098986280215817</v>
       </c>
       <c r="D16" t="n">
-        <v>15.35522660014746</v>
+        <v>2.495224322523963</v>
       </c>
       <c r="E16" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F16" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>55.10159208212524</v>
+        <v>8.954008713345353</v>
       </c>
       <c r="D17" t="n">
-        <v>9.467122964954029</v>
+        <v>1.53840748180503</v>
       </c>
       <c r="E17" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F17" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>64.15718872454939</v>
+        <v>10.42554316773928</v>
       </c>
       <c r="D18" t="n">
-        <v>13.40611995119509</v>
+        <v>2.178494492069203</v>
       </c>
       <c r="E18" t="n">
-        <v>16.48509817449919</v>
+        <v>2.678828453356119</v>
       </c>
       <c r="F18" t="n">
-        <v>12.62404676748363</v>
+        <v>2.05140759971609</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
